--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -24399,118 +24399,517 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>狂犬病</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO135" t="inlineStr">
+      <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP135" t="inlineStr">
+      <c r="AP137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR135" t="inlineStr">
+      <c r="AR137" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS135" t="inlineStr"/>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV135" t="inlineStr">
+      <c r="AV137" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW135" t="inlineStr">
+      <c r="AW137" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
+      <c r="AX137" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY135" t="inlineStr">
+      <c r="AY137" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
+      <c r="AZ137" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA135" t="inlineStr">
+      <c r="BA137" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB135" t="inlineStr">
+      <c r="BB137" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC135" t="inlineStr">
+      <c r="BC137" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -24632,7 +25031,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -24642,7 +25041,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -24662,7 +25061,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -22658,12 +22658,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22697,13 +22697,16 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>41</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.003043355597483661</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22736,42 +22739,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -22803,12 +22806,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22833,7 +22836,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22847,9 +22850,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22858,82 +22858,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22946,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -23012,98 +22998,23 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -23197,7 +23108,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -23232,7 +23143,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -23249,23 +23160,98 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23359,7 +23345,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -23411,98 +23397,23 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN130" t="b">
-        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -23596,7 +23507,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -23631,7 +23542,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23648,23 +23559,98 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -23758,7 +23744,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -23810,98 +23796,23 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -23995,7 +23906,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -24030,7 +23941,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -24047,23 +23958,98 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -24157,7 +24143,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -24209,98 +24195,23 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -24394,7 +24305,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -24429,7 +24340,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -24446,23 +24357,98 @@
       <c r="P135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -24556,7 +24542,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -24608,98 +24594,23 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -24793,123 +24704,360 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
         <is>
           <t>狂犬病</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="inlineStr">
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO137" t="inlineStr">
+      <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP137" t="inlineStr">
+      <c r="AP138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR137" t="inlineStr">
+      <c r="AR138" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS137" t="inlineStr"/>
-      <c r="AT137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV137" t="inlineStr">
+      <c r="AV138" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW137" t="inlineStr">
+      <c r="AW138" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
+      <c r="AX138" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY137" t="inlineStr">
+      <c r="AY138" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
+      <c r="AZ138" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA137" t="inlineStr">
+      <c r="BA138" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB137" t="inlineStr">
+      <c r="BB138" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC137" t="inlineStr">
+      <c r="BC138" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25031,7 +25179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -25041,7 +25189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -25093,7 +25241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>173</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16">
@@ -25103,7 +25251,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>162</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -20044,12 +20044,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20083,84 +20083,92 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>37</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.002477149904928561</v>
+        <v>0</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20187,17 +20195,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20236,76 +20244,165 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary human rabies notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20337,12 +20434,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20376,13 +20473,16 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>37</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>0.002477149904928561</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20415,42 +20515,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20482,12 +20582,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20512,7 +20612,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20560,42 +20660,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20627,12 +20727,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20657,7 +20757,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20671,9 +20771,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20682,82 +20779,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20784,17 +20867,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20819,7 +20902,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20833,168 +20916,76 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21026,12 +21017,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -21056,7 +21047,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -21070,6 +21061,9 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21078,68 +21072,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21174,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -21201,7 +21209,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21218,23 +21226,98 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21328,17 +21411,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21363,7 +21446,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21377,168 +21460,76 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21570,12 +21561,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21600,7 +21591,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21614,6 +21605,9 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21622,68 +21616,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21710,7 +21718,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -21745,7 +21753,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21762,23 +21770,98 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -21872,17 +21955,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21907,7 +21990,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21921,168 +22004,76 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22114,12 +22105,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -22144,7 +22135,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -22158,6 +22149,9 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22166,68 +22160,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22254,7 +22262,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -22289,7 +22297,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22306,23 +22314,98 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -22416,17 +22499,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22451,7 +22534,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22465,168 +22548,76 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22658,12 +22649,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22688,68 +22679,82 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.003043355597483661</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -22759,22 +22764,22 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22801,17 +22806,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22836,12 +22841,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -22850,76 +22855,168 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22951,12 +23048,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22981,7 +23078,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22990,73 +23087,59 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>41</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.003043355597483661</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -23066,22 +23149,22 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -23108,17 +23191,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -23143,7 +23226,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -23157,168 +23240,76 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23371,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -23542,7 +23533,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23779,7 +23770,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23941,7 +23932,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -24178,7 +24169,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -24340,7 +24331,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -24577,7 +24568,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -24739,7 +24730,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -24946,118 +24937,517 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
         <is>
           <t>狂犬病</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="inlineStr">
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO138" t="inlineStr">
+      <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP138" t="inlineStr">
+      <c r="AP140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
+      <c r="AR140" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS138" t="inlineStr"/>
-      <c r="AT138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV138" t="inlineStr">
+      <c r="AV140" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW138" t="inlineStr">
+      <c r="AW140" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
+      <c r="AX140" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY138" t="inlineStr">
+      <c r="AY140" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
+      <c r="AZ140" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA138" t="inlineStr">
+      <c r="BA140" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB138" t="inlineStr">
+      <c r="BB140" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC138" t="inlineStr">
+      <c r="BC140" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25179,7 +25569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -25189,7 +25579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -25209,7 +25599,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -25453,6 +25453,405 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25486,7 +25885,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25968,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -25579,7 +25978,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -25599,7 +25998,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -23196,12 +23196,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -23274,42 +23274,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23341,12 +23341,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -23385,9 +23385,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23396,82 +23393,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23498,7 +23481,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -23550,98 +23533,23 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -23735,7 +23643,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -23770,7 +23678,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23787,23 +23695,98 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -23897,7 +23880,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -23949,98 +23932,23 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -24134,7 +24042,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -24169,7 +24077,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -24186,23 +24094,98 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -24296,7 +24279,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -24348,98 +24331,23 @@
       <c r="P135" t="n">
         <v>0</v>
       </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -24533,7 +24441,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -24568,7 +24476,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -24585,23 +24493,98 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -24695,7 +24678,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -24747,98 +24730,23 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -24932,7 +24840,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -24967,7 +24875,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24984,23 +24892,98 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -25094,7 +25077,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -25146,98 +25129,23 @@
       <c r="P139" t="n">
         <v>0</v>
       </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -25331,17 +25239,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25366,12 +25274,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N140" t="n">
@@ -25380,76 +25288,168 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25481,12 +25481,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -25525,9 +25525,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -25536,82 +25533,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25638,7 +25621,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -25690,98 +25673,23 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -25847,6 +25755,642 @@
         </is>
       </c>
       <c r="BC142" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25885,7 +26429,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -25968,7 +26512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -25978,7 +26522,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -25998,7 +26542,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -37216,6 +37216,550 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37249,7 +37793,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -37332,7 +37876,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -37342,7 +37886,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -37362,7 +37906,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4838,6 +4973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5373,6 +5513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5518,6 +5663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5666,6 +5816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6368,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6760,6 +6920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7307,6 +7472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7854,6 +8024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7999,6 +8174,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8135,6 +8315,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8271,6 +8456,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8407,6 +8597,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8543,6 +8738,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8679,6 +8879,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8815,6 +9020,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8951,6 +9161,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9087,6 +9302,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9223,6 +9443,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9359,6 +9584,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9495,6 +9725,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9631,6 +9866,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9767,6 +10007,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9903,6 +10148,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10039,6 +10289,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10175,6 +10430,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10311,6 +10571,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10447,6 +10712,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10583,6 +10853,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10719,6 +10994,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10855,6 +11135,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10991,6 +11276,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11127,6 +11417,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11263,6 +11558,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11399,6 +11699,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11535,6 +11840,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12064,6 +12374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12599,6 +12914,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13143,6 +13463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13291,6 +13616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13838,6 +14168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14385,6 +14720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14932,6 +15272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15470,6 +15815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15615,6 +15965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16159,6 +16514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16307,6 +16667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16854,6 +17219,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17401,6 +17771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17948,6 +18323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18492,6 +18872,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18637,6 +19022,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18773,6 +19163,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18909,6 +19304,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19045,6 +19445,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19181,6 +19586,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19317,6 +19727,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19453,6 +19868,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19589,6 +20009,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19725,6 +20150,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19861,6 +20291,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19997,6 +20432,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20133,6 +20573,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20269,6 +20714,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20405,6 +20855,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20541,6 +20996,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20677,6 +21137,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20813,6 +21278,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20949,6 +21419,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21085,6 +21560,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21221,6 +21701,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21357,6 +21842,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21493,6 +21983,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21629,6 +22124,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21765,6 +22265,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21901,6 +22406,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22037,6 +22547,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22173,6 +22688,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22702,6 +23222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22847,6 +23372,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22992,6 +23522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23140,6 +23675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23687,6 +24227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24234,6 +24779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24781,6 +25331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25718,6 +26273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26633,6 +27193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26778,6 +27343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26926,6 +27496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27473,6 +28048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28020,6 +28600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28567,6 +29152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29114,6 +29704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30051,6 +30646,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33286,6 +33886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33431,6 +34036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33576,6 +34186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34120,6 +34735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34664,6 +35284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35208,6 +35833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36145,6 +36775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39765,6 +40400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39910,6 +40550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40055,6 +40700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40599,6 +41249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41143,6 +41798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41687,6 +42347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42179,12 +42844,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -42218,84 +42883,92 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q251" t="n">
-        <v>41</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.003043355597483661</v>
+        <v>0</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42322,17 +42995,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -42371,9 +43044,34 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -42381,6 +43079,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary human rabies notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -42388,7 +43144,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -42398,55 +43154,55 @@
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CA_ON_PHO_IDTO_RABIES_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42473,17 +43229,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -42517,39 +43273,20 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>狂犬病</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>43</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>41</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.003043355597483661</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -42557,130 +43294,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
-      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -42712,12 +43387,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -42751,10 +43426,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -42826,7 +43501,7 @@
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
@@ -42863,12 +43538,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -42902,10 +43577,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -42949,7 +43624,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -43060,7 +43735,7 @@
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
@@ -43097,12 +43772,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -43136,10 +43811,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O256" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43211,7 +43886,7 @@
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
@@ -43248,12 +43923,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -43287,10 +43962,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -43334,7 +44009,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -43445,7 +44120,7 @@
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
@@ -43482,12 +44157,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -43521,10 +44196,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O258" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -43596,7 +44271,7 @@
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
@@ -43633,12 +44308,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -43672,10 +44347,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -43719,7 +44394,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -43830,7 +44505,7 @@
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
@@ -43867,12 +44542,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -43906,21 +44581,16 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43933,7 +44603,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -43943,15 +44613,15 @@
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -43986,7 +44656,7 @@
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
@@ -44023,12 +44693,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -44062,10 +44732,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -44109,7 +44779,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -44167,7 +44837,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -44177,15 +44847,15 @@
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -44220,7 +44890,7 @@
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
@@ -44257,12 +44927,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -44296,16 +44966,21 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44318,7 +44993,7 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
@@ -44328,15 +45003,15 @@
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -44371,7 +45046,7 @@
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
@@ -44408,12 +45083,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -44447,10 +45122,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U263" t="inlineStr">
         <is>
@@ -44494,7 +45169,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -44552,7 +45227,7 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ263" t="inlineStr">
@@ -44562,15 +45237,15 @@
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -44605,7 +45280,7 @@
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
@@ -44642,12 +45317,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -44681,21 +45356,16 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44708,7 +45378,7 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ264" t="inlineStr">
@@ -44718,15 +45388,15 @@
       </c>
       <c r="AS264" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -44761,7 +45431,7 @@
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
@@ -44798,12 +45468,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -44837,10 +45507,10 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -44884,7 +45554,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -44942,7 +45612,7 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
@@ -44952,15 +45622,15 @@
       </c>
       <c r="AS265" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_RABIES</t>
+          <t>SER_CN_PROV_DC_RABIES; SER_CN_PROV_REPORT_RABIES</t>
         </is>
       </c>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -44995,7 +45665,7 @@
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
@@ -45032,12 +45702,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -45076,76 +45746,87 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="R266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45172,17 +45853,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -45221,76 +45902,165 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="R267" t="n">
-        <v>0</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_RABIES</t>
+        </is>
+      </c>
       <c r="AT267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45322,12 +46092,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -45352,7 +46122,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -45366,9 +46136,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="P268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -45377,82 +46144,73 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -45479,17 +46237,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -45514,7 +46272,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -45528,168 +46286,81 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="P269" t="n">
-        <v>0</v>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45751,7 +46422,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -45913,7 +46584,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -46150,7 +46821,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -46312,7 +46983,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -46549,7 +47220,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -46711,7 +47382,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -46948,7 +47619,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -47110,7 +47781,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -47317,12 +47988,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -47347,12 +48018,12 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -47361,6 +48032,9 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -47369,68 +48043,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47457,7 +48145,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -47492,12 +48180,12 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -47509,23 +48197,98 @@
       <c r="P279" t="n">
         <v>0</v>
       </c>
-      <c r="R279" t="n">
-        <v>0</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>SER_JP_RABIES_WEEKLY</t>
         </is>
       </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
@@ -47619,17 +48382,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -47654,7 +48417,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -47668,168 +48431,81 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="P280" t="n">
-        <v>0</v>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN280" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ280" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr">
-        <is>
-          <t>SER_JP_RABIES_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47891,7 +48567,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -48053,7 +48729,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -48290,7 +48966,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -48452,7 +49128,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -48689,7 +49365,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -48851,7 +49527,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -49058,118 +49734,522 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G289" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>Rabies</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
         <is>
           <t>狂犬病</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K289" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="L289" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N287" t="n">
-        <v>0</v>
-      </c>
-      <c r="O287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>0</v>
-      </c>
-      <c r="S287" t="inlineStr">
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO287" t="inlineStr">
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP287" t="inlineStr">
+      <c r="AP289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR287" t="inlineStr">
+      <c r="AR289" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS287" t="inlineStr"/>
-      <c r="AT287" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU287" t="inlineStr">
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV287" t="inlineStr">
+      <c r="AV289" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW287" t="inlineStr">
+      <c r="AW289" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX287" t="inlineStr">
+      <c r="AX289" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY287" t="inlineStr">
+      <c r="AY289" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ287" t="inlineStr">
+      <c r="AZ289" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA287" t="inlineStr">
+      <c r="BA289" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB287" t="inlineStr">
+      <c r="BB289" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC287" t="inlineStr">
+      <c r="BC289" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -49291,7 +50371,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -49301,7 +50381,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -49321,7 +50401,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d019/2026-2029.xlsx
+++ b/diseases/d019/2026-2029.xlsx
@@ -50255,6 +50255,405 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>rabies</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Japan NIID rabies notifications, distinct from other lyssavirus infections.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_JP_RABIES_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50288,7 +50687,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -50371,7 +50770,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -50381,7 +50780,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
@@ -50401,7 +50800,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
